--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -751,7 +751,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1079,10 +1079,8 @@
           <t>Rishi Kant Parajuli</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9846210952</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9846210952</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1097,10 +1095,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9846210952</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9846210952</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -1117,10 +1113,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.69458</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.69458</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -1176,25 +1170,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.27214</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.27213999999999</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,36 +528,54 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -572,10 +590,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -612,23 +630,69 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>IPTV Issue</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -643,12 +707,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -659,10 +724,15 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -671,27 +741,49 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C4" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -705,11 +797,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -754,9 +846,9 @@
     <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="28" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
     <col width="18" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
@@ -1218,6 +1310,438 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:25 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" s="3" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr"/>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr"/>
+      <c r="AA3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AC3" s="3" t="inlineStr"/>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr"/>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr"/>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr"/>
+      <c r="AM3" s="3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:20 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AC4" s="3" t="inlineStr"/>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:18 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr"/>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr"/>
+      <c r="AA5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AC5" s="3" t="inlineStr"/>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr"/>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr"/>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr"/>
+      <c r="AM5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:05 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr"/>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AC6" s="3" t="inlineStr"/>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,54 +528,90 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B6" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>20.0%</t>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -634,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -657,10 +693,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -669,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -680,19 +716,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -707,13 +743,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -724,15 +762,25 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -741,7 +789,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -750,40 +798,124 @@
       <c r="C2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="F3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Other / Uncategorized</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -797,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX6"/>
+  <dimension ref="A1:AX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -808,26 +940,26 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="27" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
@@ -837,13 +969,13 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="19" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -1742,6 +1874,870 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:40 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>slow internet</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339279</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Gokul Kumar Jha</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Gokul Kumar Jha</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9761148007</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:40:06 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>LTP9761148007</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:18:42 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:40:06 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Manakamana Jewellers, dhapakhel, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>jhag3854@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>High Latency</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Kiran Khadka</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>A02-CDB1</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>14h 21m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:39 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338976</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Abishek Deuja</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Abishek Deuja</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9860476919</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:39:55 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9860476919</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:33:22 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:39:55 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.71485</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Panchamukhi Hanuman Temple, Kharibot, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>deujaabhishek@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>04:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Shristi Shrestha</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L20-7</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.35709</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>19h 6m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:44 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338693</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Pradip Tamang</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Pradip Tamang</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9818819737</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:08:56 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9808460153</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:34:58 AM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:44:21 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.70483</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Near Everest Bank Limited ???????? ?????, Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>pt2087077@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>08:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>1,8</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.27583</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>13h 35m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>23h 9m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:43 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338693</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Pradip Tamang</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Pradip Tamang</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9818819737</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:08:56 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9808460153</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:34:58 AM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:44:21 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.70483</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Near Everest Bank Limited ???????? ?????, Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>pt2087077@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>08:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>1,8</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.27583</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>13h 35m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>23h 9m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX10"/>
+  <dimension ref="A1:AX11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -975,7 +975,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -1941,10 +1941,8 @@
           <t>Gokul Kumar Jha</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9761148007</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9761148007</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1979,10 +1977,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -2038,25 +2034,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>A02-CDB1</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2157,10 +2149,8 @@
           <t>Abishek Deuja</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9860476919</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9860476919</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2195,10 +2185,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.71485</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.71485</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2254,25 +2242,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L20-7</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.35709</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.35709</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2373,10 +2357,8 @@
           <t>Pradip Tamang</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9818819737</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9818819737</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2411,10 +2393,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.70483</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.70483</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2470,25 +2450,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>1,8</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.27583</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.27583</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2589,10 +2565,8 @@
           <t>Pradip Tamang</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9818819737</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9818819737</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2627,10 +2601,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.70483</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.70483</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2686,47 +2658,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>1,8</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.27583</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.27583</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>13h 35m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>23h 9m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS10" s="3" t="inlineStr">
-        <is>
-          <t>13h 35m</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="inlineStr">
-        <is>
-          <t>23h 9m</t>
-        </is>
-      </c>
-      <c r="AU10" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV10" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
@@ -2735,6 +2703,114 @@
       <c r="AX10" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:01 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : router nt working   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
+      <c r="AA11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AC11" s="3" t="inlineStr"/>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr"/>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr"/>
+      <c r="AN11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : router nt working   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX11"/>
+  <dimension ref="A1:AX15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2814,6 +2814,438 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:16 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade the Router   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr"/>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr"/>
+      <c r="V12" s="3" t="inlineStr"/>
+      <c r="W12" s="3" t="inlineStr"/>
+      <c r="X12" s="3" t="inlineStr"/>
+      <c r="Y12" s="3" t="inlineStr"/>
+      <c r="Z12" s="3" t="inlineStr"/>
+      <c r="AA12" s="3" t="inlineStr"/>
+      <c r="AB12" s="3" t="inlineStr"/>
+      <c r="AC12" s="3" t="inlineStr"/>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr"/>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr"/>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr"/>
+      <c r="AM12" s="3" t="inlineStr"/>
+      <c r="AN12" s="3" t="inlineStr"/>
+      <c r="AO12" s="3" t="inlineStr"/>
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade the Router   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:26 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr"/>
+      <c r="V13" s="3" t="inlineStr"/>
+      <c r="W13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="inlineStr"/>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr"/>
+      <c r="AA13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AC13" s="3" t="inlineStr"/>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
+      <c r="AM13" s="3" t="inlineStr"/>
+      <c r="AN13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:28 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr"/>
+      <c r="V14" s="3" t="inlineStr"/>
+      <c r="W14" s="3" t="inlineStr"/>
+      <c r="X14" s="3" t="inlineStr"/>
+      <c r="Y14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr"/>
+      <c r="AA14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="AC14" s="3" t="inlineStr"/>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr"/>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr"/>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="3" t="inlineStr"/>
+      <c r="AN14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:27 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr"/>
+      <c r="V15" s="3" t="inlineStr"/>
+      <c r="W15" s="3" t="inlineStr"/>
+      <c r="X15" s="3" t="inlineStr"/>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr"/>
+      <c r="AA15" s="3" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AC15" s="3" t="inlineStr"/>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr"/>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr"/>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr"/>
+      <c r="AM15" s="3" t="inlineStr"/>
+      <c r="AN15" s="3" t="inlineStr"/>
+      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -582,36 +582,54 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>35.7%</t>
+      <c r="B7" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -670,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -693,10 +711,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -705,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
     </row>
@@ -728,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>5.6%</t>
         </is>
       </c>
     </row>
@@ -743,15 +761,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -777,10 +796,15 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -802,16 +826,19 @@
         <v>0</v>
       </c>
       <c r="E2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="6" t="n">
-        <v>1</v>
+      <c r="G2" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -824,23 +851,26 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -848,14 +878,17 @@
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -865,57 +898,116 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>5</v>
+      <c r="E9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -929,59 +1021,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX15"/>
+  <dimension ref="A1:AX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="31" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="31" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="27" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="30" customWidth="1" min="32" max="32"/>
-    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="19" customWidth="1" min="38" max="38"/>
-    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="28" customWidth="1" min="47" max="47"/>
+    <col width="32" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
-    <col width="18" customWidth="1" min="50" max="50"/>
+    <col width="23" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3246,6 +3338,830 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:51 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339133</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Chalachitra Chautari pvt.ltd</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Chalachitra Chautari pvt.ltd</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9867020120</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:51:45 AM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>chalachitra_fttx</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:49:47 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:51:45 AM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr"/>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>kalikasthan dillibzar	, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>High Latency</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>02:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Bhumika Saud</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>CDB258</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>18h 1m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:54 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Frequent disconnection</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339241</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Chaudhary</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Chaudhary</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9746625579</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:30:16 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>KLK9746625579</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 07:30:28 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:54:35 AM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>27.72239895777987,85.29581583282115, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>naomidon07@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Due to Optical Power flapping</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>CDB165</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>15h 24m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>16h 24m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:51 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339348</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Keshav Basnet</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Keshav Basnet</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9851335109</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:35:54 AM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>KLK9851335109</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:43:28 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:51:00 AM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Balaju Chowk - Historical landmark P8G3+RR5 Balaju Roundabout Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>keshabb788@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>CDB194</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>2h 15m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>14h 7m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:50 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339348</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Keshav Basnet</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Keshav Basnet</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9851335109</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:35:54 AM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>KLK9851335109</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:43:28 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:51:00 AM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Balaju Chowk - Historical landmark P8G3+RR5 Balaju Roundabout Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>keshabb788@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>CDB194</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>2h 15m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>14h 7m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.4%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>21.1%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>26.3%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.3%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -848,22 +848,22 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -888,7 +888,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -913,14 +913,14 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -938,17 +938,17 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -998,7 +998,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>1</v>
@@ -1007,7 +1007,7 @@
         <v>4</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX19"/>
+  <dimension ref="A1:AX20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1032,7 +1032,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="31" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -1050,7 +1050,7 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="34" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
@@ -3405,10 +3405,8 @@
           <t>Chalachitra Chautari pvt.ltd</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9867020120</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9867020120</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3494,10 +3492,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
@@ -3508,7 +3504,7 @@
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -3599,20 +3595,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M17" s="3" t="inlineStr"/>
       <c r="N17" s="3" t="inlineStr">
         <is>
           <t>Prabin Chaudhary</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9746625579</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9746625579</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3698,10 +3688,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
@@ -3712,7 +3700,7 @@
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -3813,10 +3801,8 @@
           <t>Keshav Basnet</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9851335109</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9851335109</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -3906,10 +3892,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
@@ -3920,7 +3904,7 @@
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4021,10 +4005,8 @@
           <t>Keshav Basnet</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9851335109</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9851335109</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4114,10 +4096,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
@@ -4128,29 +4108,29 @@
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>2h 15m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>14h 7m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
           <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS19" s="3" t="inlineStr">
-        <is>
-          <t>2h 15m</t>
-        </is>
-      </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>14h 7m</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV19" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW19" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
@@ -4159,6 +4139,222 @@
       <c r="AX19" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:12 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>not upgraded internet service</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338492</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Bikram Shrestha</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Bikram Shrestha</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9849941148</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:12:25 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9849941148</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 07:25:17 AM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:12:25 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.77456</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-customer care</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>budhanilkantha near Park Village Resort, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>biki12344@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr"/>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>L54-1</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.36075</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 47m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.0%</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -863,7 +863,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -888,7 +888,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -986,28 +986,53 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4" t="n">
+      <c r="E10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="4" t="n">
-        <v>9</v>
+      <c r="G10" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1021,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX20"/>
+  <dimension ref="A1:AX21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4209,10 +4234,8 @@
           <t>Bikram Shrestha</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9849941148</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9849941148</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4247,10 +4270,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>27.77456</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>27.77456</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -4306,55 +4327,255 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>L54-1</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.36075</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.36075</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 47m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
           <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS20" s="3" t="inlineStr">
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:18 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>slow internet issue</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338308</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Ishor Thapa</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Ishor Thapa</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9858052904</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:18:43 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9858052904</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 07:56:27 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:18:43 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Siddhicharan Marg Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>10:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Anusha Adhikari</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>L10-3</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT20" s="3" t="inlineStr">
-        <is>
-          <t>1d 4h 47m</t>
-        </is>
-      </c>
-      <c r="AU20" s="3" t="inlineStr">
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 22m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV20" s="3" t="inlineStr">
-        <is>
-          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW20" s="3" t="inlineStr">
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX20" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>10</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.6%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>23.8%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.8%</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -863,7 +863,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -888,7 +888,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -913,7 +913,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -963,7 +963,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -988,7 +988,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1001,38 +1001,63 @@
         <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>10</v>
+      <c r="F11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX21"/>
+  <dimension ref="A1:AX22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4442,10 +4467,8 @@
           <t>Ishor Thapa</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9858052904</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9858052904</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4531,10 +4554,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
@@ -4545,29 +4566,29 @@
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 22m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
           <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS21" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT21" s="3" t="inlineStr">
-        <is>
-          <t>1d 16h 22m</t>
-        </is>
-      </c>
-      <c r="AU21" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV21" s="3" t="inlineStr">
-        <is>
-          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW21" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -4576,6 +4597,214 @@
       <c r="AX21" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:32 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>one light blinking</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339492</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Mukhiya</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Mukhiya</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9849090123</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:50:08 AM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9849090123</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:07:35 AM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:32:12 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Dhimelwah Kumari Marg Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>grg42589@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI22" s="3" t="inlineStr"/>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>2h 42m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>3h 24m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4667,10 +4667,8 @@
           <t>Shanta Mukhiya</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9849090123</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9849090123</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4742,10 +4740,8 @@
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="AH22" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH22" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI22" s="3" t="inlineStr"/>
       <c r="AJ22" s="3" t="inlineStr"/>
@@ -4760,10 +4756,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
@@ -4774,7 +4768,7 @@
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : one light blinking   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>27.3%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>22.7%</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
@@ -813,17 +813,17 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
@@ -832,26 +832,26 @@
         <v>0</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -1051,13 +1051,13 @@
         <v>2</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>5</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX22"/>
+  <dimension ref="A1:AX23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4802,6 +4802,214 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 1:08 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339755</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Saubhagya Group</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Saubhagya Group</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9846860411</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:08:01 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>LTP9845908326</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:49:50 AM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:08:01 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr"/>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>King's Akabare Jhol MoMo - Momo restaurant M8PP+P5 Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>support@saubhagyagroup.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1h 18m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -829,10 +829,10 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1054,10 +1054,10 @@
         <v>3</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX23"/>
+  <dimension ref="A1:AX25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4869,10 +4869,8 @@
           <t>Saubhagya Group</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9846860411</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9846860411</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -4962,10 +4960,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
@@ -4976,29 +4972,29 @@
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1h 18m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
           <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS23" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT23" s="3" t="inlineStr">
-        <is>
-          <t>1h 18m</t>
-        </is>
-      </c>
-      <c r="AU23" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV23" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW23" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -5007,6 +5003,430 @@
       <c r="AX23" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 1:16 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338846</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Raju Maharjan</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Raju Maharjan</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9841582320</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:22:55 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9841582320</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:22:55 PM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:16:13 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.675955</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Chandragiri ward no:10,Boshigau,near Basic Learning English Secondary School, Bagmati, Central, Nep</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr"/>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>06:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>CDB461</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.247036</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 1:15 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338846</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Raju Maharjan</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Raju Maharjan</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9841582320</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:22:55 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9841582320</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:22:55 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:16:13 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.675955</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Chandragiri ward no:10,Boshigau,near Basic Learning English Secondary School, Bagmati, Central, Nep</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr"/>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>06:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>CDB461</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.247036</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>7</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>2</v>
@@ -832,29 +832,29 @@
         <v>1</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>2</v>
@@ -863,11 +863,11 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -876,19 +876,19 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="G4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -913,7 +913,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -1045,10 +1045,10 @@
         <v>1</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>3</v>
@@ -1057,7 +1057,7 @@
         <v>6</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX25"/>
+  <dimension ref="A1:AX28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5073,10 +5073,8 @@
           <t>Raju Maharjan</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9841582320</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9841582320</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5111,10 +5109,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.675955</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.675955</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -5166,25 +5162,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>CDB461</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.247036</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.24703599999999</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -5285,10 +5277,8 @@
           <t>Raju Maharjan</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9841582320</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9841582320</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5323,10 +5313,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>27.675955</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>27.675955</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -5378,53 +5366,577 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>CDB461</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.247036</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.24703599999999</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS25" s="3" t="inlineStr">
-        <is>
-          <t>23h 53m</t>
-        </is>
-      </c>
-      <c r="AT25" s="3" t="inlineStr">
-        <is>
-          <t>23h 53m</t>
-        </is>
-      </c>
-      <c r="AU25" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV25" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW25" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
       <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 1:22 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : red light blinking   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>red light blinking</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338795</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Bir chakra Thapa</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Bir chakra Thapa</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9851020871</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:22:40 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9851020871</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:48:01 PM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:22:40 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.748214</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Gairi Gaun Futsal Park, Nagarjun 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr"/>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>07:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>L9-5</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.32077</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : red light blinking   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>1d 34m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : red light blinking   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 1:17 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338833</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Kopila Poudel Bhattarai</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Kopila Poudel Bhattarai</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9851136564</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:17:24 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>BKT9851136564</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:15:28 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:17:24 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>P94C+8GF, Bhaimal Margh Chowk, Kathmandu 44600 near by Easy Mart, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>yatirajbhattarai@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>06:45 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>L31-7</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr"/>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>1d 1m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 1:23 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
+      <c r="N28" s="3" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr"/>
+      <c r="V28" s="3" t="inlineStr"/>
+      <c r="W28" s="3" t="inlineStr"/>
+      <c r="X28" s="3" t="inlineStr"/>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr"/>
+      <c r="AA28" s="3" t="inlineStr"/>
+      <c r="AB28" s="3" t="inlineStr"/>
+      <c r="AC28" s="3" t="inlineStr"/>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr"/>
+      <c r="AF28" s="3" t="inlineStr"/>
+      <c r="AG28" s="3" t="inlineStr"/>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr"/>
+      <c r="AM28" s="3" t="inlineStr"/>
+      <c r="AN28" s="3" t="inlineStr"/>
+      <c r="AO28" s="3" t="inlineStr"/>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>17.9%</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>21.4%</t>
         </is>
       </c>
     </row>
@@ -826,13 +826,13 @@
         <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1051,13 +1051,13 @@
         <v>3</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>6</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX28"/>
+  <dimension ref="A1:AX29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5481,10 +5481,8 @@
           <t>Bir chakra Thapa</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9851020871</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9851020871</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5519,10 +5517,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>27.748214</t>
-        </is>
+      <c r="Y26" s="3" t="n">
+        <v>27.748214</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -5574,25 +5570,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>L9-5</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.32077</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.32077</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : red light blinking   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -5693,10 +5685,8 @@
           <t>Kopila Poudel Bhattarai</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9851136564</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9851136564</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -5786,10 +5776,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
@@ -5800,7 +5788,7 @@
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -5942,6 +5930,226 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 1:41 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339545</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Binesh Joshi</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Binesh Joshi</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9840166838</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:41:01 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9843499802</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:46:47 AM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:41:01 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>27.68433</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu ,Shankhamul, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>CDB668</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>85.33969</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>3h 54m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>61.3%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>32.3%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>16.1%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>19.4%</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -888,7 +888,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>Setup Box Recovery</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -898,22 +898,22 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -963,7 +963,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -988,7 +988,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1013,7 +1013,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1026,38 +1026,88 @@
         <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="4" t="n">
+      <c r="C13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="D13" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F13" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G11" s="4" t="n">
-        <v>16</v>
+      <c r="G13" s="4" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX29"/>
+  <dimension ref="A1:AX32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5997,10 +6047,8 @@
           <t>Binesh Joshi</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9840166838</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9840166838</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6035,10 +6083,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t>27.68433</t>
-        </is>
+      <c r="Y29" s="3" t="n">
+        <v>27.68433</v>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
@@ -6076,10 +6122,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH29" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH29" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
@@ -6098,55 +6142,691 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
           <t>CDB668</t>
         </is>
       </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>85.33969</t>
-        </is>
+      <c r="AP29" s="3" t="n">
+        <v>85.33969</v>
       </c>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>3h 54m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS29" s="3" t="inlineStr">
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 1:50 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : smart tv youtube issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>smart tv youtube issue</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338933</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Bhandari</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Bhandari</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9851320036</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:50:06 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>BKT9851320036</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:44:35 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:50:06 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>Near By Bode, Madhyapur Thimi 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>05:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>L28-5</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : smart tv youtube issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT29" s="3" t="inlineStr">
-        <is>
-          <t>3h 54m</t>
-        </is>
-      </c>
-      <c r="AU29" s="3" t="inlineStr">
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>23h 5m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV29" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW29" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX29" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : smart tv youtube issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 1:58 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : set up box collection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>set up box collection</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337661</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Shrestha</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Shrestha</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9849110228</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:58:39 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9849110228</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:27:26 PM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:58:39 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>27.76959</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Tokha Near By Tokha Ganeshthan Mandir,02, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>bjshresthaa500@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Setup Box Recovery</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>17:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Bajgain</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>L27-4</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>85.329</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : set up box collection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 31m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : set up box collection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 1:57 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : new package  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>new package</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335171</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Som Shrestha</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Som Shrestha</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9840062889</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:57:37 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9840062889</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:02:09 PM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:57:37 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.76023</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-customer care</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Near Sadbhab Banquet, Tokha Rd, Tokha-03, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>somshrestha3669@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Setup Box Recovery</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>16:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr"/>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>L42-1</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.329</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : new package  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>4d 15h 55m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : new package  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>64.7%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.4%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>14.7%</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>23.5%</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
@@ -826,13 +826,13 @@
         <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -863,20 +863,20 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>Setup Box Recovery</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -888,20 +888,20 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Setup Box Recovery</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -913,11 +913,11 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -938,14 +938,14 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -954,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1</v>
@@ -963,14 +963,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>1</v>
@@ -988,7 +988,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1013,7 +1013,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1038,7 +1038,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -1051,10 +1051,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>1</v>
@@ -1063,20 +1063,20 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1086,28 +1086,53 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="4" t="n">
+      <c r="B14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="C14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" s="4" t="n">
+      <c r="E14" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G13" s="4" t="n">
-        <v>19</v>
+      <c r="G14" s="4" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1121,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX32"/>
+  <dimension ref="A1:AX35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6257,10 +6282,8 @@
           <t>Roshan Bhandari</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9851320036</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9851320036</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -6350,10 +6373,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
@@ -6364,7 +6385,7 @@
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : smart tv youtube issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
@@ -6455,20 +6476,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M31" s="3" t="inlineStr"/>
       <c r="N31" s="3" t="inlineStr">
         <is>
           <t>Bijay Shrestha</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9849110228</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9849110228</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -6503,10 +6518,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>27.76959</t>
-        </is>
+      <c r="Y31" s="3" t="n">
+        <v>27.76959</v>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
@@ -6562,25 +6575,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>L27-4</t>
         </is>
       </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>85.329</t>
-        </is>
+      <c r="AP31" s="3" t="n">
+        <v>85.32899999999999</v>
       </c>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : set up box collection   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -6681,10 +6690,8 @@
           <t>Som Shrestha</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9840062889</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9840062889</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -6719,10 +6726,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.76023</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.76023</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -6778,55 +6783,695 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>L42-1</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.329</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.32899999999999</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>4d 15h 55m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
           <t>Case : new package  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS32" s="3" t="inlineStr">
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 2:12 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339474</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Mabhendra sahi</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Mabhendra sahi</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9700048213</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:12:42 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9827757657</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 08:54:39 AM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:12:42 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>27.66029377081862, 85.35606862323932 GPS Coordinates Nearest: CDB457 (61m Road) Map: CG Imadole, Bag</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr"/>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>CDB456</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr"/>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>4d 15h 55m</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>5h 18m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV32" s="3" t="inlineStr">
-        <is>
-          <t>Case : new package  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW32" s="3" t="inlineStr">
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 2:07 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g name not showing   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>5g name not showing</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338698</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Birendra Yadav</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Birendra Yadav</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9817780679</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:07:20 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9817780679</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:38:14 AM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:07:20 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>27.68416</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>27.67567408847685, 85.32718108233304 GPS Coordinates Nearest: CDB643 (16m Road) Map: CG Kupandole, B</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>by856338@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>08:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>CDB233</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>85.32352</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g name not showing   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 29m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g name not showing   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX32" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 2:06 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339313</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Rahisha Tamrakar</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Rahisha Tamrakar</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9843807398</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:06:16 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9843807398</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:55:19 PM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:06:16 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>27.67113</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>27.67113, 85.3247, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>tamrakarrahisha@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>4,7</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>85.3247</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>17h 10m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>30.6%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>27.8%</t>
         </is>
       </c>
     </row>
@@ -829,10 +829,10 @@
         <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -1129,10 +1129,10 @@
         <v>5</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1146,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX35"/>
+  <dimension ref="A1:AX37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6898,10 +6898,8 @@
           <t>Mabhendra sahi</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9700048213</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9700048213</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -6987,10 +6985,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
@@ -7001,7 +6997,7 @@
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
@@ -7102,10 +7098,8 @@
           <t>Birendra Yadav</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9817780679</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9817780679</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -7140,10 +7134,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>27.68416</t>
-        </is>
+      <c r="Y34" s="3" t="n">
+        <v>27.68416</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -7181,10 +7173,8 @@
           <t>Configuration Issue</t>
         </is>
       </c>
-      <c r="AH34" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH34" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
@@ -7203,25 +7193,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>CDB233</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>85.32352</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>85.32352</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>Case : 5g name not showing   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
@@ -7322,10 +7308,8 @@
           <t>Rahisha Tamrakar</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9843807398</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9843807398</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -7360,10 +7344,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t>27.67113</t>
-        </is>
+      <c r="Y35" s="3" t="n">
+        <v>27.67113</v>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
@@ -7401,10 +7383,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH35" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH35" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
@@ -7423,47 +7403,43 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>4,7</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>85.3247</t>
-        </is>
+      <c r="AP35" s="3" t="n">
+        <v>85.32470000000001</v>
       </c>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>17h 10m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
           <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS35" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT35" s="3" t="inlineStr">
-        <is>
-          <t>17h 10m</t>
-        </is>
-      </c>
-      <c r="AU35" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV35" s="3" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="AW35" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -7472,6 +7448,438 @@
       <c r="AX35" s="3" t="inlineStr">
         <is>
           <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 2:18 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338564</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Basnet</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Basnet</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9861435546</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:25:57 AM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9861435546</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:25:57 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:18:15 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.670011</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Daju bhai mart, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>9861435546@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>CDB265</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.249608</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 2:17 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338564</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Basnet</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Basnet</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9861435546</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:25:57 AM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9861435546</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:25:57 AM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:18:15 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.670011</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Daju bhai mart, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>9861435546@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>CDB265</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.249608</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>24</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>64.9%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>29.7%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.5%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.0%</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX37"/>
+  <dimension ref="A1:AX38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1192,7 +1192,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7518,10 +7518,8 @@
           <t>Sunil Basnet</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9861435546</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9861435546</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7556,10 +7554,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>27.670011</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>27.670011</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -7615,25 +7611,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>CDB265</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.249608</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.24960799999999</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -7734,10 +7726,8 @@
           <t>Sunil Basnet</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9861435546</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9861435546</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -7772,10 +7762,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="inlineStr">
-        <is>
-          <t>27.670011</t>
-        </is>
+      <c r="Y37" s="3" t="n">
+        <v>27.670011</v>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
@@ -7831,47 +7819,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>CDB265</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.249608</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.24960799999999</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS37" s="3" t="inlineStr">
-        <is>
-          <t>1d 4h 52m</t>
-        </is>
-      </c>
-      <c r="AT37" s="3" t="inlineStr">
-        <is>
-          <t>1d 4h 52m</t>
-        </is>
-      </c>
-      <c r="AU37" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV37" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW37" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -7880,6 +7864,114 @@
       <c r="AX37" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 2:35 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr"/>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr"/>
+      <c r="M38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="inlineStr"/>
+      <c r="O38" s="3" t="inlineStr"/>
+      <c r="P38" s="3" t="inlineStr"/>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr"/>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr"/>
+      <c r="V38" s="3" t="inlineStr"/>
+      <c r="W38" s="3" t="inlineStr"/>
+      <c r="X38" s="3" t="inlineStr"/>
+      <c r="Y38" s="3" t="inlineStr"/>
+      <c r="Z38" s="3" t="inlineStr"/>
+      <c r="AA38" s="3" t="inlineStr"/>
+      <c r="AB38" s="3" t="inlineStr"/>
+      <c r="AC38" s="3" t="inlineStr"/>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr"/>
+      <c r="AF38" s="3" t="inlineStr"/>
+      <c r="AG38" s="3" t="inlineStr"/>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr"/>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr"/>
+      <c r="AM38" s="3" t="inlineStr"/>
+      <c r="AN38" s="3" t="inlineStr"/>
+      <c r="AO38" s="3" t="inlineStr"/>
+      <c r="AP38" s="3" t="inlineStr"/>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX38" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>9</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>31.0%</t>
         </is>
       </c>
     </row>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
@@ -829,10 +829,10 @@
         <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -888,20 +888,20 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -926,13 +926,13 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -963,14 +963,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>1</v>
@@ -988,14 +988,14 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -1004,7 +1004,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1013,11 +1013,11 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0</v>
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -1063,7 +1063,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -1076,10 +1076,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -1088,7 +1088,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
@@ -1111,28 +1111,78 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" s="4" t="n">
+      <c r="B16" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="D16" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>23</v>
+      <c r="E16" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1146,7 +1196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX38"/>
+  <dimension ref="A1:AX43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1192,7 +1242,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7975,6 +8025,1046 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 3:02 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>SLOW ISSUE</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338844</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Kalpana Baral</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Kalpana Baral</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9842684993</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:38:58 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>BKT9842684993</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:22:07 PM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:02:01 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>Bhaktapur Futsal - Futsal court MC96+P25 Araniko Highway Suryabinayak 44800, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>9842684993@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr"/>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>L31-6</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>1d 23m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 39m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX39" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 2:54 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV remote issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>IPTV remote issue</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339979</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Bhujel</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Bhujel</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9744235441</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:54:21 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>9744235441</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:34:26 PM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:54:21 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr"/>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Police Station, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr"/>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>L32-8</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr"/>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV remote issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>1h 19m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV remote issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX40" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 2:59 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340084</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Raju Maharjan</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Raju Maharjan</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9841582320</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:59:20 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9841582320</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:41:35 PM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:59:20 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.675955</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Chandragiri ward no:10,Boshigau,near Basic Learning English Secondary School, Bagmati, Central, Nep</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr"/>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>CDB461</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.247036</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>17m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX41" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 2:57 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Skycom to net TV  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>Skycom to net TV</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338449</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Sadik Aakhtar Ansari</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Sadik Aakhtar Ansari</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9813761666</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:38:45 AM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>9851244184</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 06:34:55 AM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:57:12 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>27.732722</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Ganga Hall Marg Kathmandu 44600 near by Kohinoor School - University, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>ss93official@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr"/>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Parajuli</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>2,8</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>85.304031</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Skycom to net TV  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 18m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>1d 8h 22m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Skycom to net TV  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX42" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 2:55 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337927</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Madhav Traders</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Madhav Traders</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9745867186</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:55:53 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9745867186</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:32:21 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:55:53 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr"/>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>Madhav Traders, MAKUTE PROFESSIONAL POWER TOOLS - Hardware store ?? ??????? ?????, Kathmandu 44600,</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>agchirag0811@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>14:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr"/>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 23m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>28.9%</t>
         </is>
       </c>
     </row>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>17.8%</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.9%</t>
         </is>
       </c>
     </row>
@@ -761,10 +761,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -838,23 +838,23 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>2</v>
@@ -863,23 +863,23 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Setup Box Recovery</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>2</v>
@@ -888,23 +888,23 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>2</v>
@@ -913,20 +913,20 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>Setup Box Recovery</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -938,14 +938,14 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -954,23 +954,23 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>1</v>
@@ -988,14 +988,14 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -1013,14 +1013,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -1063,7 +1063,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -1088,14 +1088,14 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>0</v>
@@ -1104,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>1</v>
@@ -1113,11 +1113,11 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>0</v>
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>1</v>
@@ -1138,7 +1138,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
@@ -1148,10 +1148,10 @@
         <v>0</v>
       </c>
       <c r="D15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>0</v>
@@ -1161,28 +1161,78 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C16" s="4" t="n">
+      <c r="B18" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="C18" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E16" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F16" s="4" t="n">
+      <c r="F18" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="4" t="n">
-        <v>28</v>
+      <c r="G18" s="4" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1196,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX43"/>
+  <dimension ref="A1:AX46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1231,7 +1281,7 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="30" customWidth="1" min="32" max="32"/>
-    <col width="32" customWidth="1" min="33" max="33"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -8092,10 +8142,8 @@
           <t>Kalpana Baral</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9842684993</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9842684993</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -8181,10 +8229,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
@@ -8195,7 +8241,7 @@
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>Case : SLOW ISSUE   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
@@ -8296,10 +8342,8 @@
           <t>Sujan Bhujel</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9744235441</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9744235441</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -8385,10 +8429,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
@@ -8399,7 +8441,7 @@
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV remote issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
@@ -8500,10 +8542,8 @@
           <t>Raju Maharjan</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9841582320</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9841582320</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -8538,10 +8578,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t>27.675955</t>
-        </is>
+      <c r="Y41" s="3" t="n">
+        <v>27.675955</v>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
@@ -8593,25 +8631,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>CDB461</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.247036</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.24703599999999</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
@@ -8702,20 +8736,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M42" s="3" t="inlineStr"/>
       <c r="N42" s="3" t="inlineStr">
         <is>
           <t>Sadik Aakhtar Ansari</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9813761666</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9813761666</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -8750,10 +8778,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t>27.732722</t>
-        </is>
+      <c r="Y42" s="3" t="n">
+        <v>27.732722</v>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
@@ -8805,25 +8831,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>2,8</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>85.304031</t>
-        </is>
+      <c r="AP42" s="3" t="n">
+        <v>85.30403099999999</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : Skycom to net TV  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
@@ -8924,10 +8946,8 @@
           <t>Madhav Traders</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9745867186</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9745867186</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -9017,10 +9037,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
@@ -9031,37 +9049,685 @@
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 23m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
           <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS43" s="3" t="inlineStr">
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 3:21 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339147</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Keshab pariyar</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Keshab pariyar</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9763494932</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:21:02 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>BKT9763494932</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 06:06:53 PM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:21:02 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-CG Group</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>bhaktapur , Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>abc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>01:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Hareram Pandit</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT43" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 23m</t>
-        </is>
-      </c>
-      <c r="AU43" s="3" t="inlineStr">
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>21h 14m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV43" s="3" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW43" s="3" t="inlineStr">
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX44" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 3:31 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV Issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Net TV Issue</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339263</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Magar</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Magar</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9813664152</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:31:28 PM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9813664152</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 07:50:17 PM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:31:28 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>27.70515</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>P842+3W9, ???????: ?????, Kathmandu 44600 near Paropakar Furniture, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>sabinmagar4152@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>00:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr"/>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>4,11</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>85.302205</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV Issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>19h 41m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV Issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX45" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 3:22 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336061</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Shakti Kumar Godar</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Shakti Kumar Godar</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9855053649</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:22:28 PM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>9855053649</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 06:29:28 PM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:22:28 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>27.743596</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>Tokha ward no:11,near Nirmal Batika Academy, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>godarshaktikumar7@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>07:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>2,14</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>85.31971</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>3d 20h 53m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX43" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AX46" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.0%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>9</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.8%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.0%</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.8%</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>2</v>
@@ -832,13 +832,13 @@
         <v>3</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -848,16 +848,16 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G3" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -888,23 +888,23 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>2</v>
@@ -1217,10 +1217,10 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>6</v>
@@ -1232,7 +1232,7 @@
         <v>9</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1246,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX46"/>
+  <dimension ref="A1:AX48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9146,10 +9146,8 @@
           <t>Keshab pariyar</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9763494932</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9763494932</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -9184,10 +9182,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
@@ -9247,25 +9243,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>1,1</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -9366,10 +9358,8 @@
           <t>Sabin Magar</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9813664152</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9813664152</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -9404,10 +9394,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>27.70515</t>
-        </is>
+      <c r="Y45" s="3" t="n">
+        <v>27.70515</v>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
@@ -9463,25 +9451,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>4,11</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>85.302205</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>85.302205</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>Case : Net TV Issue  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
@@ -9582,10 +9566,8 @@
           <t>Shakti Kumar Godar</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9855053649</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9855053649</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -9620,10 +9602,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>27.743596</t>
-        </is>
+      <c r="Y46" s="3" t="n">
+        <v>27.743596</v>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
@@ -9679,55 +9659,479 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
           <t>2,14</t>
         </is>
       </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>85.31971</t>
-        </is>
+      <c r="AP46" s="3" t="n">
+        <v>85.31971</v>
       </c>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>3d 20h 53m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS46" s="3" t="inlineStr">
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX46" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 3:42 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339778</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Kishan Manandhar</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Kishan Manandhar</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9823489535</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:42:51 PM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9823489535</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:04:35 PM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:42:51 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>27.6782</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>Near 6/9 Khaja Ghar, Madhyapur Thimi, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>kishanmanandhar26@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>L63-3</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>85.38727</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT46" s="3" t="inlineStr">
-        <is>
-          <t>3d 20h 53m</t>
-        </is>
-      </c>
-      <c r="AU46" s="3" t="inlineStr">
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>3h 38m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV46" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW46" s="3" t="inlineStr">
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX46" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AX47" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 3:36 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>Net TV</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339347</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Bikram Gajurel</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Bikram Gajurel</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9803749646</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:36:57 PM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>9803749646</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:43:03 PM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:36:57 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>27.70089</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>kwahiti marga near suzuki showroom and near siddhi ganesh motorcycle workshop teku, Bagmati, Central</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>vgajurel@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr"/>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr"/>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>4,14</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>85.30298</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>17h 53m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
     </row>
@@ -826,13 +826,13 @@
         <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -1226,13 +1226,13 @@
         <v>6</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>9</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1246,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX48"/>
+  <dimension ref="A1:AX49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1280,7 +1280,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="32" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -9774,10 +9774,8 @@
           <t>Kishan Manandhar</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9823489535</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9823489535</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -9812,10 +9810,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y47" s="3" t="inlineStr">
-        <is>
-          <t>27.6782</t>
-        </is>
+      <c r="Y47" s="3" t="n">
+        <v>27.6782</v>
       </c>
       <c r="Z47" s="3" t="inlineStr">
         <is>
@@ -9871,25 +9867,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
           <t>L63-3</t>
         </is>
       </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>85.38727</t>
-        </is>
+      <c r="AP47" s="3" t="n">
+        <v>85.38727</v>
       </c>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
@@ -9990,10 +9982,8 @@
           <t>Bikram Gajurel</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9803749646</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9803749646</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -10028,10 +10018,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>27.70089</t>
-        </is>
+      <c r="Y48" s="3" t="n">
+        <v>27.70089</v>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
@@ -10083,55 +10071,259 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
           <t>4,14</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>85.30298</t>
-        </is>
+      <c r="AP48" s="3" t="n">
+        <v>85.30298000000001</v>
       </c>
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>17h 53m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
           <t>Case : Net TV  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS48" s="3" t="inlineStr">
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 3:58 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337833</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Sumitra Shrestha</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Sumitra Shrestha</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9841482102</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:58:35 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9841482102S</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:50:28 PM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:58:35 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr"/>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Ratna Rajya Sec. School, M8WP+7XM, Devkota Sadak, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>sumitrashrestha1444@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>15:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>L52-6</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr"/>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT48" s="3" t="inlineStr">
-        <is>
-          <t>17h 53m</t>
-        </is>
-      </c>
-      <c r="AU48" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV48" s="3" t="inlineStr">
-        <is>
-          <t>Case : Net TV  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW48" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AX48" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 8m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>32</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>65.3%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.3%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX49"/>
+  <dimension ref="A1:AX50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1292,7 +1292,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -10186,10 +10186,8 @@
           <t>Sumitra Shrestha</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9841482102</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9841482102</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -10279,10 +10277,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
@@ -10293,29 +10289,29 @@
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 8m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS49" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT49" s="3" t="inlineStr">
-        <is>
-          <t>2d 1h 8m</t>
-        </is>
-      </c>
-      <c r="AU49" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV49" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW49" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -10324,6 +10320,114 @@
       <c r="AX49" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 3:59 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr"/>
+      <c r="J50" s="3" t="inlineStr"/>
+      <c r="K50" s="3" t="inlineStr"/>
+      <c r="L50" s="3" t="inlineStr"/>
+      <c r="M50" s="3" t="inlineStr"/>
+      <c r="N50" s="3" t="inlineStr"/>
+      <c r="O50" s="3" t="inlineStr"/>
+      <c r="P50" s="3" t="inlineStr"/>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr"/>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr"/>
+      <c r="V50" s="3" t="inlineStr"/>
+      <c r="W50" s="3" t="inlineStr"/>
+      <c r="X50" s="3" t="inlineStr"/>
+      <c r="Y50" s="3" t="inlineStr"/>
+      <c r="Z50" s="3" t="inlineStr"/>
+      <c r="AA50" s="3" t="inlineStr"/>
+      <c r="AB50" s="3" t="inlineStr"/>
+      <c r="AC50" s="3" t="inlineStr"/>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr"/>
+      <c r="AF50" s="3" t="inlineStr"/>
+      <c r="AG50" s="3" t="inlineStr"/>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr"/>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr"/>
+      <c r="AM50" s="3" t="inlineStr"/>
+      <c r="AN50" s="3" t="inlineStr"/>
+      <c r="AO50" s="3" t="inlineStr"/>
+      <c r="AP50" s="3" t="inlineStr"/>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX50" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.0%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.0%</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>32.0%</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>2</v>
@@ -832,7 +832,7 @@
         <v>3</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -1220,7 +1220,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>6</v>
@@ -1232,7 +1232,7 @@
         <v>9</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1246,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX50"/>
+  <dimension ref="A1:AX51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1292,7 +1292,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -10431,6 +10431,214 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 4:24 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339911</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>tej krishna shrestha</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>tej krishna shrestha</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9860466835</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:05 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>CHB9860466835</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:58:18 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:05 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr"/>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>Chapabot, Gothatar Chapabot, Gothatar - Historical landmark P95M+269 Kageshwori Manohara 44600, Kath</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>9841659170@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>2,10</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr"/>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>3h 25m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX51" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>29.4%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>15.7%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>31.4%</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
@@ -832,7 +832,7 @@
         <v>3</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>8</v>
@@ -1232,7 +1232,7 @@
         <v>9</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1246,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX51"/>
+  <dimension ref="A1:AX52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1259,10 +1259,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="31" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="31" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -10498,10 +10498,8 @@
           <t>tej krishna shrestha</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9860466835</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9860466835</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -10591,10 +10589,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
@@ -10605,37 +10601,245 @@
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>3h 25m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS51" s="3" t="inlineStr">
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX51" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 4:33 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339837</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Tripathiand brothers Automobile pvt ltd</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Tripathiand brothers Automobile pvt ltd</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9851351926</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:33:19 PM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>LTP9851351926</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:25:46 PM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:33:19 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr"/>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>27.684280386708334, 85.30324177112256, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr">
+        <is>
+          <t>9851351926@GIMAL.COM</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>3,7</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr"/>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT51" s="3" t="inlineStr">
-        <is>
-          <t>3h 25m</t>
-        </is>
-      </c>
-      <c r="AU51" s="3" t="inlineStr">
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>4h 7m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV51" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW51" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX51" s="3" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>64.8%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>14.8%</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>31.5%</t>
         </is>
       </c>
     </row>
@@ -826,13 +826,13 @@
         <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -1226,13 +1226,13 @@
         <v>6</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>9</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1246,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX52"/>
+  <dimension ref="A1:AX55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10702,10 +10702,8 @@
           <t>Tripathiand brothers Automobile pvt ltd</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9851351926</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9851351926</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -10795,10 +10793,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
@@ -10809,37 +10805,469 @@
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>4h 7m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS52" s="3" t="inlineStr">
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 4:24 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339757</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Padam Bahadur Karki</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Padam Bahadur Karki</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9843233935</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:28 PM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>9843233935</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:51:40 AM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:28 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr">
+        <is>
+          <t>27.707875</t>
+        </is>
+      </c>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>27.707875, 85.323431, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>4,13</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>85.323431</t>
+        </is>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT52" s="3" t="inlineStr">
-        <is>
-          <t>4h 7m</t>
-        </is>
-      </c>
-      <c r="AU52" s="3" t="inlineStr">
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>4h 32m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV52" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW52" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AX52" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 4:52 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr"/>
+      <c r="J54" s="3" t="inlineStr"/>
+      <c r="K54" s="3" t="inlineStr"/>
+      <c r="L54" s="3" t="inlineStr"/>
+      <c r="M54" s="3" t="inlineStr"/>
+      <c r="N54" s="3" t="inlineStr"/>
+      <c r="O54" s="3" t="inlineStr"/>
+      <c r="P54" s="3" t="inlineStr"/>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr"/>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr"/>
+      <c r="V54" s="3" t="inlineStr"/>
+      <c r="W54" s="3" t="inlineStr"/>
+      <c r="X54" s="3" t="inlineStr"/>
+      <c r="Y54" s="3" t="inlineStr"/>
+      <c r="Z54" s="3" t="inlineStr"/>
+      <c r="AA54" s="3" t="inlineStr"/>
+      <c r="AB54" s="3" t="inlineStr"/>
+      <c r="AC54" s="3" t="inlineStr"/>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr"/>
+      <c r="AF54" s="3" t="inlineStr"/>
+      <c r="AG54" s="3" t="inlineStr"/>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr"/>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr"/>
+      <c r="AM54" s="3" t="inlineStr"/>
+      <c r="AN54" s="3" t="inlineStr"/>
+      <c r="AO54" s="3" t="inlineStr"/>
+      <c r="AP54" s="3" t="inlineStr"/>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX54" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 4:32 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr"/>
+      <c r="J55" s="3" t="inlineStr"/>
+      <c r="K55" s="3" t="inlineStr"/>
+      <c r="L55" s="3" t="inlineStr"/>
+      <c r="M55" s="3" t="inlineStr"/>
+      <c r="N55" s="3" t="inlineStr"/>
+      <c r="O55" s="3" t="inlineStr"/>
+      <c r="P55" s="3" t="inlineStr"/>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr"/>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr"/>
+      <c r="V55" s="3" t="inlineStr"/>
+      <c r="W55" s="3" t="inlineStr"/>
+      <c r="X55" s="3" t="inlineStr"/>
+      <c r="Y55" s="3" t="inlineStr"/>
+      <c r="Z55" s="3" t="inlineStr"/>
+      <c r="AA55" s="3" t="inlineStr"/>
+      <c r="AB55" s="3" t="inlineStr"/>
+      <c r="AC55" s="3" t="inlineStr"/>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr"/>
+      <c r="AF55" s="3" t="inlineStr"/>
+      <c r="AG55" s="3" t="inlineStr"/>
+      <c r="AH55" s="3" t="inlineStr"/>
+      <c r="AI55" s="3" t="inlineStr"/>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr"/>
+      <c r="AM55" s="3" t="inlineStr"/>
+      <c r="AN55" s="3" t="inlineStr"/>
+      <c r="AO55" s="3" t="inlineStr"/>
+      <c r="AP55" s="3" t="inlineStr"/>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX55" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.3%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.5%</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>32.7%</t>
         </is>
       </c>
     </row>
@@ -826,13 +826,13 @@
         <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -1226,13 +1226,13 @@
         <v>6</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>9</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1246,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX55"/>
+  <dimension ref="A1:AX56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10906,10 +10906,8 @@
           <t>Padam Bahadur Karki</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9843233935</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9843233935</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -10944,10 +10942,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y53" s="3" t="inlineStr">
-        <is>
-          <t>27.707875</t>
-        </is>
+      <c r="Y53" s="3" t="n">
+        <v>27.707875</v>
       </c>
       <c r="Z53" s="3" t="inlineStr">
         <is>
@@ -11003,25 +10999,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
           <t>4,13</t>
         </is>
       </c>
-      <c r="AP53" s="3" t="inlineStr">
-        <is>
-          <t>85.323431</t>
-        </is>
+      <c r="AP53" s="3" t="n">
+        <v>85.323431</v>
       </c>
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
@@ -11271,6 +11263,218 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 5:15 PM</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340092</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh rai</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh rai</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>9818733606</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 05:15:01 PM</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>9818733606</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:46:23 PM</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 05:15:01 PM</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y56" s="3" t="inlineStr">
+        <is>
+          <t>27.696071</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC56" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="inlineStr"/>
+      <c r="AE56" s="3" t="inlineStr">
+        <is>
+          <t>New baneshwor shanti binayek tole Madan bhandari, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF56" s="3" t="inlineStr"/>
+      <c r="AG56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="inlineStr"/>
+      <c r="AI56" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ56" s="3" t="inlineStr"/>
+      <c r="AK56" s="3" t="inlineStr"/>
+      <c r="AL56" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>L56-2</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr">
+        <is>
+          <t>85.331197</t>
+        </is>
+      </c>
+      <c r="AQ56" s="3" t="inlineStr"/>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>2h 28m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX56" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.1%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.8%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>33.9%</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
@@ -832,7 +832,7 @@
         <v>3</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>8</v>
@@ -1232,7 +1232,7 @@
         <v>9</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1246,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX56"/>
+  <dimension ref="A1:AX57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -11330,10 +11330,8 @@
           <t>Dinesh rai</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>9818733606</t>
-        </is>
+      <c r="O56" s="3" t="n">
+        <v>9818733606</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
@@ -11368,10 +11366,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y56" s="3" t="inlineStr">
-        <is>
-          <t>27.696071</t>
-        </is>
+      <c r="Y56" s="3" t="n">
+        <v>27.696071</v>
       </c>
       <c r="Z56" s="3" t="inlineStr">
         <is>
@@ -11423,55 +11419,267 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN56" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
           <t>L56-2</t>
         </is>
       </c>
-      <c r="AP56" s="3" t="inlineStr">
-        <is>
-          <t>85.331197</t>
-        </is>
+      <c r="AP56" s="3" t="n">
+        <v>85.331197</v>
       </c>
       <c r="AQ56" s="3" t="inlineStr"/>
       <c r="AR56" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>2h 28m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS56" s="3" t="inlineStr">
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX56" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 5:20 PM</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>WIFI6 Upgrade</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340062</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>KTM Ply Trade PVT LTD</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>KTM Ply Trade PVT LTD</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>9801894210</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 05:20:03 PM</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>9801894210</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:27:12 PM</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 05:20:03 PM</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y57" s="3" t="inlineStr">
+        <is>
+          <t>27.67779</t>
+        </is>
+      </c>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA57" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB57" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC57" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD57" s="3" t="inlineStr"/>
+      <c r="AE57" s="3" t="inlineStr">
+        <is>
+          <t>Near Motorhead Bikes Nepal, Nayabato Chwok, Dhobighat, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF57" s="3" t="inlineStr">
+        <is>
+          <t>ktmplytrade@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG57" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH57" s="3" t="inlineStr"/>
+      <c r="AI57" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ57" s="3" t="inlineStr"/>
+      <c r="AK57" s="3" t="inlineStr"/>
+      <c r="AL57" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM57" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN57" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO57" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP57" s="3" t="inlineStr">
+        <is>
+          <t>85.30252</t>
+        </is>
+      </c>
+      <c r="AQ57" s="3" t="inlineStr"/>
+      <c r="AR57" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT56" s="3" t="inlineStr">
-        <is>
-          <t>2h 28m</t>
-        </is>
-      </c>
-      <c r="AU56" s="3" t="inlineStr">
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>2h 52m</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV56" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW56" s="3" t="inlineStr">
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW57" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX56" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AX57" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_20_Sep_2026.xlsx
@@ -1292,7 +1292,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -11534,10 +11534,8 @@
           <t>KTM Ply Trade PVT LTD</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>9801894210</t>
-        </is>
+      <c r="O57" s="3" t="n">
+        <v>9801894210</v>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
@@ -11572,10 +11570,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y57" s="3" t="inlineStr">
-        <is>
-          <t>27.67779</t>
-        </is>
+      <c r="Y57" s="3" t="n">
+        <v>27.67779</v>
       </c>
       <c r="Z57" s="3" t="inlineStr">
         <is>
@@ -11631,25 +11627,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN57" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN57" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
           <t>3,5</t>
         </is>
       </c>
-      <c r="AP57" s="3" t="inlineStr">
-        <is>
-          <t>85.30252</t>
-        </is>
+      <c r="AP57" s="3" t="n">
+        <v>85.30252</v>
       </c>
       <c r="AQ57" s="3" t="inlineStr"/>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
